--- a/research/crisis-bench/results/审改-场景要点.xlsx
+++ b/research/crisis-bench/results/审改-场景要点.xlsx
@@ -1303,7 +1303,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>分配、部署、救援队、卫星电话、优先、力量</t>
+          <t>分配、部署、救援队、卫星电话</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
@@ -10083,24 +10083,12 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>15分钟、约15、一刻钟、15分、十余分钟</t>
-        </is>
-      </c>
-      <c r="H217" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="I217" t="inlineStr">
-        <is>
-          <t>答案泄漏：匹配词 15分钟 已直接出现在情报原文</t>
-        </is>
-      </c>
-      <c r="J217" t="inlineStr">
-        <is>
-          <t>改用未泄漏的等价数值区间，或调整情报使目标数字不直接出现</t>
-        </is>
-      </c>
+          <t>15分钟内将威胁、约15分钟到达、15分钟内蔓延、一刻钟、15分内</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
+      <c r="J217" t="inlineStr"/>
       <c r="K217" t="inlineStr"/>
       <c r="L217" t="inlineStr"/>
     </row>
@@ -16659,24 +16647,12 @@
       </c>
       <c r="G365" t="inlineStr">
         <is>
-          <t>135公斤、一百多公斤、百来公斤、口粮、135人</t>
-        </is>
-      </c>
-      <c r="H365" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="I365" t="inlineStr">
-        <is>
-          <t>答案泄漏：匹配词 135人 已直接出现在情报原文</t>
-        </is>
-      </c>
-      <c r="J365" t="inlineStr">
-        <is>
-          <t>改用未泄漏的等价数值区间，或调整情报使目标数字不直接出现</t>
-        </is>
-      </c>
+          <t>135公斤、一百多公斤、百来公斤、口粮</t>
+        </is>
+      </c>
+      <c r="H365" t="inlineStr"/>
+      <c r="I365" t="inlineStr"/>
+      <c r="J365" t="inlineStr"/>
       <c r="K365" t="inlineStr"/>
       <c r="L365" t="inlineStr"/>
     </row>
@@ -24111,24 +24087,12 @@
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>3吨、饮水、补给、增援、需求、1500</t>
-        </is>
-      </c>
-      <c r="H533" s="2" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="I533" t="inlineStr">
-        <is>
-          <t>答案泄漏：匹配词 1500 已直接出现在情报原文</t>
-        </is>
-      </c>
-      <c r="J533" t="inlineStr">
-        <is>
-          <t>改用未泄漏的等价数值区间，或调整情报使目标数字不直接出现</t>
-        </is>
-      </c>
+          <t>3吨、饮水、增援</t>
+        </is>
+      </c>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
       <c r="K533" t="inlineStr"/>
       <c r="L533" t="inlineStr"/>
     </row>
@@ -33838,7 +33802,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
